--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -349,7 +349,7 @@
 </t>
   </si>
   <si>
-    <t>Type of email | type de messagerie électronique</t>
+    <t>Champs permettant de préciser le type d'email (MSSANTE | APICRYPT | OSM | AutreMessagerie) dont il est question dans le cas où le point de contact est un email.</t>
   </si>
   <si>
     <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,9 @@
     <t>Champs permettant de préciser le type d'email (MSSANTE | APICRYPT | OSM | AutreMessagerie) dont il est question dans le cas où le point de contact est un email.</t>
   </si>
   <si>
-    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
+    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
++ This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
     <t>ContactPoint.system</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-contact-point.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
